--- a/_generic/NewsPaperAds.xlsx
+++ b/_generic/NewsPaperAds.xlsx
@@ -5,14 +5,12 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="StampPaper" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="Tasks" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="Mail-In" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="Mail-Out" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="Tasks-Transmission" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="Mail-In" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="Mail-Out" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -24,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="172">
   <si>
     <t xml:space="preserve">Date</t>
   </si>
@@ -90,48 +88,6 @@
   </si>
   <si>
     <t xml:space="preserve">https://www.express.com.pk/epaper/index.aspx?Issue=NP_LHE&amp;Page=Classified_PageC007&amp;Date=20260530&amp;Pageno=7&amp;View=1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Principle Task</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CoTicker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CoName</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sub Task</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SubTask Step 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transmission of Shares</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EHL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Engro Holdings Limited Formerly: Engro Corporation Limited</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Publish newspaper ad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prepare newspaper ad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Get quote from publisher</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Receive quotation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Issue go-ahead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pick newspaper on date of publication of ad</t>
   </si>
   <si>
     <t xml:space="preserve">From</t>
@@ -587,6 +543,9 @@
     <t xml:space="preserve">JSCGL- KEL – 2603</t>
   </si>
   <si>
+    <t xml:space="preserve">RGL158522037</t>
+  </si>
+  <si>
     <t xml:space="preserve">8 Securities submitted for Book Entry Conversion rejected
     1. K-Electric Limited (KEL)- Folio # 17380</t>
   </si>
@@ -617,37 +576,20 @@
     <t xml:space="preserve">IB, pn, eng, urdu, submitted for transmission</t>
   </si>
   <si>
-    <t xml:space="preserve">userID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">uName</t>
-  </si>
-  <si>
-    <t xml:space="preserve">processID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pName</t>
-  </si>
-  <si>
-    <t xml:space="preserve">requestID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rTitle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rDateRequested</t>
-  </si>
-  <si>
-    <t xml:space="preserve">currentStateID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ilyas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transmission</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Initiate Transmission</t>
+    <t xml:space="preserve">LCI-AKZO-LCPL-61463-2603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RGL158522055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmission of Shares and Unclaimed Dividends of Late Mohammad Ayub Khan against Folio #: 61463 
+    1. LUCKY CORE INDUSTRIES LIMITED (FORMERLY: ICI PAKISTAN LIMITED)
+    2. AKZO NOBEL PAKISTAN LIMITED
+    3. LOTTE CHEMICAL PAKISTAN LIMITED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">distinctive Number corrigendum-PN
+Signature of guar1, 2 and applicant</t>
   </si>
 </sst>
 </file>
@@ -790,7 +732,7 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -1123,128 +1065,461 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="3" width="20.77"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="3" width="19.24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="3" width="36.76"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="7" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="7" width="12.92"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="8" width="12.92"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="8" width="14.93"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="9" width="45.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="9" width="37.1"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="8" style="8" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="C1" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="9" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
+      <c r="G1" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="H1" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="C2" s="3" t="s">
+    </row>
+    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="7" t="n">
+        <v>46155</v>
+      </c>
+      <c r="C2" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="F2" s="9" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="E3" s="3" t="s">
+      <c r="G2" s="9" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="E4" s="3" t="s">
+      <c r="H2" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="7" t="n">
+        <v>46155</v>
+      </c>
+      <c r="C3" s="8" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="E5" s="3" t="s">
+      <c r="F3" s="9" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="E6" s="3" t="s">
+      <c r="G3" s="9" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="E7" s="3" t="s">
+      <c r="H3" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="7" t="n">
+        <v>46156</v>
+      </c>
+      <c r="C4" s="8" t="s">
         <v>35</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="H4" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="7" t="n">
+        <v>46156</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="H5" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="7" t="n">
+        <v>46158</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="G6" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="H6" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="7" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="H7" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="7" t="n">
+        <v>46163</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="G8" s="9" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="7" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="G9" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="H9" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="7" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="G10" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="H10" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="113.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="7" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="G11" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="H11" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="113.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="7" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="G12" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="H12" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="7" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="G13" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="H13" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="7" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="G14" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="H14" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="7" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="F15" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="G15" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="H15" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="113.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="7" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="F16" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="G16" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="H16" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="7" t="n">
+        <v>45069</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="E17" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="G17" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="H17" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="7" t="n">
+        <v>46171</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="E18" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="F18" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="H18" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="7" t="n">
+        <v>46172</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="E19" s="9" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="7" t="n">
+        <v>46172</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="E20" s="9" t="s">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -1263,485 +1538,12 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="7" width="11.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="7" width="12.92"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="8" width="12.92"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="8" width="14.93"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="9" width="45.44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="9" width="37.1"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="8" style="8" width="11.53"/>
-  </cols>
-  <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="7" t="n">
-        <v>46155</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="F2" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="G2" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="H2" s="8" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="7" t="n">
-        <v>46155</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="F3" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="G3" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="H3" s="8" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="7" t="n">
-        <v>46156</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="F4" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="G4" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="H4" s="8" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="7" t="n">
-        <v>46156</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="F5" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="G5" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="H5" s="8" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="7" t="n">
-        <v>46158</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="G6" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="H6" s="8" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="7" t="n">
-        <v>46160</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="G7" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="H7" s="8" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="7" t="n">
-        <v>46163</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="E8" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="F8" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="G8" s="9" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="7" t="n">
-        <v>46163</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="E9" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="F9" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="G9" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="H9" s="8" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="7" t="n">
-        <v>46149</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="E10" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="F10" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="G10" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="H10" s="8" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="113.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="7" t="n">
-        <v>46149</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="E11" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="F11" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="G11" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="H11" s="8" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="113.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="7" t="n">
-        <v>46149</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="E12" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="F12" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="G12" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="H12" s="8" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="7" t="n">
-        <v>46165</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="E13" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="F13" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="G13" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="H13" s="8" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="7" t="n">
-        <v>46165</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="D14" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="E14" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="F14" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="G14" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="H14" s="8" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="7" t="n">
-        <v>46165</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="D15" s="8" t="s">
-        <v>95</v>
-      </c>
-      <c r="E15" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="F15" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="G15" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="H15" s="8" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="113.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="7" t="n">
-        <v>46165</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="E16" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="F16" s="10" t="s">
-        <v>101</v>
-      </c>
-      <c r="G16" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="H16" s="8" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="7" t="n">
-        <v>45069</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="D17" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="E17" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="G17" s="9" t="s">
-        <v>105</v>
-      </c>
-      <c r="H17" s="8" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="7" t="n">
-        <v>46171</v>
-      </c>
-      <c r="B18" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="C18" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="D18" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="E18" s="9" t="s">
-        <v>109</v>
-      </c>
-      <c r="F18" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="H18" s="8" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="7" t="n">
-        <v>46172</v>
-      </c>
-      <c r="B19" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="C19" s="8" t="s">
-        <v>111</v>
-      </c>
-      <c r="D19" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="E19" s="9" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="7" t="n">
-        <v>46172</v>
-      </c>
-      <c r="B20" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="C20" s="8" t="s">
-        <v>111</v>
-      </c>
-      <c r="E20" s="9" t="s">
-        <v>114</v>
-      </c>
-    </row>
-  </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="2" min="1" style="7" width="11.53"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="3" min="3" style="8" width="11.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="8" width="17.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="9" width="17.88"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="8" width="5.52"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="8" width="15.25"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="10" width="33.39"/>
@@ -1751,31 +1553,31 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>117</v>
+        <v>23</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>103</v>
       </c>
       <c r="E1" s="8" t="s">
         <v>7</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="G1" s="10" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1783,19 +1585,19 @@
         <v>46156</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="D2" s="8" t="s">
-        <v>119</v>
+        <v>29</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>105</v>
       </c>
       <c r="E2" s="8" t="n">
         <v>150</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>121</v>
+        <v>107</v>
       </c>
       <c r="I2" s="8" t="n">
         <v>1</v>
@@ -1806,19 +1608,19 @@
         <v>46156</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>122</v>
+        <v>32</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>108</v>
       </c>
       <c r="E3" s="8" t="n">
         <v>60</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="I3" s="8" t="n">
         <v>1</v>
@@ -1829,19 +1631,19 @@
         <v>46157</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>126</v>
+        <v>111</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>112</v>
       </c>
       <c r="E4" s="8" t="n">
         <v>60</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="I4" s="8" t="n">
         <v>1</v>
@@ -1852,16 +1654,16 @@
         <v>46157</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="E5" s="8" t="n">
         <v>0</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>130</v>
+        <v>116</v>
       </c>
       <c r="I5" s="8" t="n">
         <v>1</v>
@@ -1872,25 +1674,25 @@
         <v>46158</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="E6" s="8" t="n">
         <v>60</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="G6" s="12" t="s">
-        <v>134</v>
+        <v>120</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>135</v>
+        <v>121</v>
       </c>
       <c r="I6" s="8" t="n">
         <v>1</v>
@@ -1901,22 +1703,22 @@
         <v>46163</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>136</v>
+        <v>47</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>122</v>
       </c>
       <c r="E7" s="8" t="n">
         <v>60</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="H7" s="9" t="s">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="I7" s="8" t="n">
         <v>1</v>
@@ -1927,19 +1729,19 @@
         <v>46163</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>141</v>
+        <v>127</v>
       </c>
       <c r="H8" s="13" t="s">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="I8" s="8" t="n">
         <v>1</v>
@@ -1950,22 +1752,22 @@
         <v>46164</v>
       </c>
       <c r="B9" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="F9" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="C9" s="8" t="s">
-        <v>143</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>144</v>
-      </c>
-      <c r="F9" s="8" t="s">
-        <v>145</v>
-      </c>
       <c r="G9" s="10" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="H9" s="9" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
       <c r="I9" s="8" t="n">
         <v>1</v>
@@ -1976,19 +1778,19 @@
         <v>46167</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>148</v>
+        <v>61</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>134</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>149</v>
+        <v>135</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>150</v>
+        <v>136</v>
       </c>
       <c r="I10" s="8" t="n">
         <v>1</v>
@@ -1999,19 +1801,19 @@
         <v>46167</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>151</v>
+        <v>61</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>137</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>152</v>
+        <v>138</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>153</v>
+        <v>139</v>
       </c>
       <c r="I11" s="8" t="n">
         <v>1</v>
@@ -2022,19 +1824,19 @@
         <v>46167</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>154</v>
+        <v>77</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>140</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>155</v>
+        <v>141</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>150</v>
+        <v>136</v>
       </c>
       <c r="I12" s="8" t="n">
         <v>1</v>
@@ -2045,19 +1847,19 @@
         <v>46167</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>156</v>
+        <v>77</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>142</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>152</v>
+        <v>138</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>153</v>
+        <v>139</v>
       </c>
       <c r="I13" s="8" t="n">
         <v>1</v>
@@ -2068,19 +1870,19 @@
         <v>46167</v>
       </c>
       <c r="B14" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C14" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="C14" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="D14" s="8" t="s">
-        <v>157</v>
+      <c r="D14" s="9" t="s">
+        <v>143</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>150</v>
+        <v>136</v>
       </c>
       <c r="I14" s="8" t="n">
         <v>1</v>
@@ -2091,19 +1893,19 @@
         <v>46167</v>
       </c>
       <c r="B15" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C15" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="C15" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="D15" s="8" t="s">
-        <v>159</v>
+      <c r="D15" s="9" t="s">
+        <v>145</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>152</v>
+        <v>138</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>153</v>
+        <v>139</v>
       </c>
       <c r="I15" s="8" t="n">
         <v>1</v>
@@ -2114,22 +1916,22 @@
         <v>46167</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>160</v>
+        <v>146</v>
       </c>
       <c r="C16" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="D16" s="8" t="s">
-        <v>161</v>
+      <c r="D16" s="9" t="s">
+        <v>147</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>162</v>
+        <v>148</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>163</v>
+        <v>149</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>164</v>
+        <v>150</v>
       </c>
       <c r="I16" s="8" t="n">
         <v>1</v>
@@ -2140,19 +1942,19 @@
         <v>46172</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="D17" s="8" t="s">
-        <v>108</v>
+        <v>93</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>94</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>165</v>
+        <v>151</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="I17" s="8" t="n">
         <v>1</v>
@@ -2163,19 +1965,19 @@
         <v>46172</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>111</v>
-      </c>
-      <c r="D18" s="8" t="s">
-        <v>167</v>
+        <v>97</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>153</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>168</v>
+        <v>154</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>169</v>
+        <v>155</v>
       </c>
       <c r="I18" s="8" t="n">
         <v>1</v>
@@ -2186,16 +1988,19 @@
         <v>46174</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>170</v>
+        <v>156</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>171</v>
+        <v>157</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>158</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>172</v>
+        <v>159</v>
       </c>
       <c r="I19" s="8" t="n">
         <v>1</v>
@@ -2206,19 +2011,19 @@
         <v>46174</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>170</v>
-      </c>
-      <c r="D20" s="8" t="s">
-        <v>171</v>
+        <v>156</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>157</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>173</v>
+        <v>160</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>172</v>
+        <v>159</v>
       </c>
       <c r="I20" s="8" t="n">
         <v>1</v>
@@ -2229,19 +2034,22 @@
         <v>46174</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>174</v>
-      </c>
-      <c r="D21" s="8" t="s">
-        <v>175</v>
+        <v>161</v>
+      </c>
+      <c r="D21" s="9" t="s">
+        <v>162</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>176</v>
+        <v>163</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>177</v>
+        <v>164</v>
+      </c>
+      <c r="I21" s="8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2249,19 +2057,48 @@
         <v>46174</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>160</v>
+        <v>146</v>
       </c>
       <c r="C22" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="D22" s="8" t="s">
-        <v>178</v>
+      <c r="D22" s="9" t="s">
+        <v>165</v>
       </c>
       <c r="G22" s="10" t="s">
-        <v>179</v>
+        <v>166</v>
       </c>
       <c r="H22" s="9" t="s">
-        <v>180</v>
+        <v>167</v>
+      </c>
+      <c r="I22" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="7" t="n">
+        <v>46175</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D23" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="G23" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="H23" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="I23" s="8" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -2276,79 +2113,4 @@
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="3" width="7.2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="3" width="7.82"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="3" width="10.13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="3" width="12.92"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="3" width="9.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="3" width="18.94"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="3" width="15.54"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="3" width="13.69"/>
-  </cols>
-  <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="C2" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="E2" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>191</v>
-      </c>
-    </row>
-  </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
-  </headerFooter>
-</worksheet>
 </file>
--- a/_generic/NewsPaperAds.xlsx
+++ b/_generic/NewsPaperAds.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="StampPaper" sheetId="1" state="visible" r:id="rId3"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="177">
   <si>
     <t xml:space="preserve">Date</t>
   </si>
@@ -590,6 +590,21 @@
   <si>
     <t xml:space="preserve">distinctive Number corrigendum-PN
 Signature of guar1, 2 and applicant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CDCSR-LHR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SNGP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAK-SNGP-2603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmission Case - SNGPL - Late Mohammad Ayub Khan, Folio Nr: 125005252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inquired about status of transmission case, via email</t>
   </si>
 </sst>
 </file>
@@ -686,7 +701,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -741,6 +756,10 @@
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1065,7 +1084,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="7" width="11.53"/>
@@ -1521,6 +1540,13 @@
       <c r="E20" s="9" t="s">
         <v>100</v>
       </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="0"/>
+      <c r="B21" s="0"/>
+      <c r="C21" s="0"/>
+      <c r="D21" s="0"/>
+      <c r="E21" s="0"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -1538,7 +1564,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="2" min="1" style="7" width="11.53"/>
@@ -2101,6 +2127,33 @@
         <v>1</v>
       </c>
     </row>
+    <row r="24" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="7" t="n">
+        <v>46177</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="E24" s="0"/>
+      <c r="F24" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="G24" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="H24" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="I24" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="H8" r:id="rId1" display="Mr. Khalid Pervez: khalid.pervez@js.com, via PAKPOST dispatched"/>

--- a/_generic/NewsPaperAds.xlsx
+++ b/_generic/NewsPaperAds.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="181">
   <si>
     <t xml:space="preserve">Date</t>
   </si>
@@ -605,6 +605,18 @@
   </si>
   <si>
     <t xml:space="preserve">Inquired about status of transmission case, via email</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CDCSR-KHI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PSO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PSO-2606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmission of Shares and Dividends – Late Mohammad Ayub Khan,    1. Pakistan State Oil, Folio Nr: 4625 &amp; 10800</t>
   </si>
 </sst>
 </file>
@@ -758,7 +770,7 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1542,11 +1554,11 @@
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0"/>
-      <c r="B21" s="0"/>
-      <c r="C21" s="0"/>
-      <c r="D21" s="0"/>
-      <c r="E21" s="0"/>
+      <c r="A21" s="3"/>
+      <c r="B21" s="3"/>
+      <c r="C21" s="3"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -1564,7 +1576,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="2" min="1" style="7" width="11.53"/>
@@ -2140,7 +2152,7 @@
       <c r="D24" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="E24" s="0"/>
+      <c r="E24" s="3"/>
       <c r="F24" s="14" t="s">
         <v>126</v>
       </c>
@@ -2151,6 +2163,32 @@
         <v>176</v>
       </c>
       <c r="I24" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="7" t="n">
+        <v>46177</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="D25" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="F25" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="G25" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="H25" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="I25" s="8" t="n">
         <v>1</v>
       </c>
     </row>
